--- a/stories/arbres/ATOM-SOC.MET.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara monte dans le bus avec papa. Le chauffeur ouvre la porte. Papa dit : c'est un métier. Le chauffeur fait un geste utile. Il conduit. Sara dit : chauffeur. Ils descendent. Ça sent le pain chaud. Le boulanger pose les brioches. Papa dit : c'est un métier. Le boulanger fait un geste utile. Il prépare le pain. Sara dit : boulanger. Plus tard, ils passent chez le médecin. Le médecin écoute le cœur. C'est un métier. Un geste utile. Il soigne. À l'école, la maîtresse lit. C'est un métier. Un geste utile. Elle aide les enfants. Sara nomme chaque métier. Parce qu'elle nomme, elle comprend le geste.</t>
+          <t>Sara monte dans le bus avec papa. Le chauffeur ouvre la porte. C'est un métier. Le chauffeur fait un geste utile. Il conduit. Chauffeur. Ils descendent. Ça sent le pain chaud. Le boulanger pose les brioches. C'est un métier. Le boulanger fait un geste utile. Il prépare le pain. Boulanger. Plus tard, ils passent chez le médecin. Le médecin écoute le cœur. C'est un métier. Un geste utile. Il soigne. À l'école, la maîtresse lit. C'est un métier. Un geste utile. Elle aide les enfants. Sara nomme chaque métier. Parce qu'elle nomme, elle comprend le geste.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara monte dans le bus avec papa. Le chauffeur ouvre la porte.
+papa|C'est un métier.
+narrateur|Le chauffeur fait un geste utile. Il conduit.
+enfant-f|Chauffeur. Ils descendent. Ça sent le pain chaud.
+narrateur|Le boulanger pose les brioches.
+papa|C'est un métier.
+narrateur|Le boulanger fait un geste utile. Il prépare le pain.
+enfant-f|Boulanger. Plus tard, ils passent chez le médecin.
+narrateur|Le médecin écoute le cœur. C'est un métier. Un geste utile. Il soigne. À l'école, la maîtresse lit. C'est un métier. Un geste utile. Elle aide les enfants. Sara nomme chaque métier. Parce qu'elle nomme, elle comprend le geste.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le chauffeur conduit le bus. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara serre la main de papa. Ils rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,11 @@
 narrateur|Le médecin écoute le cœur. C'est un métier. Un geste utile. Il soigne. À l'école, la maîtresse lit. C'est un métier. Un geste utile. Elle aide les enfants. Sara nomme chaque métier. Parce qu'elle nomme, elle comprend le geste.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Le chauffeur conduit le bus. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Sara a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1851,7 @@
           <t>narrateur|Sara serre la main de papa. Ils rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.MET.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les métiers de Sara</t>
+          <t>Le bob de la poupée</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut consoler sa poupée, pansement décollé au genou. Chez le médecin du village, un pansement neuf pour Sarah, un tout petit pour la poupée. Pas de sang.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara monte dans le bus avec papa. Le chauffeur ouvre la porte. C'est un métier. Le chauffeur fait un geste utile. Il conduit. Chauffeur. Ils descendent. Ça sent le pain chaud. Le boulanger pose les brioches. C'est un métier. Le boulanger fait un geste utile. Il prépare le pain. Boulanger. Plus tard, ils passent chez le médecin. Le médecin écoute le cœur. C'est un métier. Un geste utile. Il soigne. À l'école, la maîtresse lit. C'est un métier. Un geste utile. Elle aide les enfants. Sara nomme chaque métier. Parce qu'elle nomme, elle comprend le geste.</t>
+          <t>La poupée penche sur la chaise de bois. Un petit pansement se décolle au genou. Le tissu est froissé, un peu gris. La chambre sent encore le linge propre. Un rayon passe sur le parquet. Sarah vit ici, avec papa. Elle a un bob, papa. Au genou de la poupée ? Oui. Je veux la consoler. Sarah pose sa main sur le genou de tissu. Le tissu est rêche, un peu froid. Le pansement ne tient plus. On va chez le médecin du village ? Pour la poupée ? Pour la poupée. Et pour toi, si ça pique. En ce moment, Sarah serre la poupée. Le bras de chiffon pend un peu. Ils descendent l'escalier de pierre. Dehors, le tilleul sent le miel. Un oiseau saute dans l'herbe. Elle a mal, je crois. On marche doucement. Tu la tiens bien ? Oui, papa. La plaque du médecin brille au soleil. Elle est ronde, un peu chaude. La porte sent le savon clair. On frappe, tout doux. Toc, toc. Le médecin ouvre. Sa blouse est blanche, un peu froissée. Ma poupée a un bob. Sarah veut la consoler. C'est le médecin. C'est son métier. Médecin. Sarah montre le genou de tissu. Le vieux pansement pend. Le médecin parle tout bas. Il soigne, Sarah. Tu restes près de moi ? Oui. Sarah a aussi un petit bob au genou. Ça pique, tout doux, rien de grave. Moi aussi, un peu. On montre, sans courir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara monte dans le bus avec papa. Le chauffeur ouvre la porte. Papa dit : c'est un &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;. Le chauffeur fait un geste utile. Il conduit. Sara dit : chauffeur. Ils descendent. Ça sent le pain chaud. Le boulanger pose les brioches. Papa dit : c'est un métier. Le boulanger fait un geste utile. Il prépare le pain. Sara dit : boulanger. Plus tard, ils passent chez le médecin. Le médecin écoute le cœur. C'est un métier. Un geste utile. Il soigne. À l'école, la maîtresse lit. C'est un métier. Un geste utile. Elle aide les enfants. Sara nomme chaque métier. Parce qu'elle nomme, elle comprend le geste.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La poupée penche sur la chaise de bois. Un petit pansement se décolle au genou. Le tissu est froissé, un peu gris. La chambre sent encore le linge propre. Un rayon passe sur le parquet. Sarah vit ici, avec papa. Elle a un bob, papa. Au genou de la poupée ? Oui. Je veux la consoler. Sarah pose sa main sur le genou de tissu. Le tissu est rêche, un peu froid. Le pansement ne tient plus. On va chez le médecin du village ? Pour la poupée ? Pour la poupée. Et pour toi, si ça pique. En ce moment, Sarah serre la poupée. Le bras de chiffon pend un peu. Ils descendent l'escalier de pierre. Dehors, le tilleul sent le miel. Un oiseau saute dans l'herbe. Elle a mal, je crois. On marche doucement. Tu la tiens bien ? Oui, papa. La plaque du médecin brille au soleil. Elle est ronde, un peu chaude. La porte sent le savon clair. On frappe, tout doux. Toc, toc. Le médecin ouvre. Sa blouse est blanche, un peu froissée. Ma poupée a un bob. Sarah veut la consoler. C'est le médecin. C'est son métier. Médecin. Sarah montre le genou de tissu. Le vieux pansement pend. Le médecin parle tout bas. Il soigne, Sarah. Tu restes près de moi ? Oui. Sarah a aussi un petit bob au genou. Ça pique, tout doux, rien de grave. Moi aussi, un peu. On montre, sans courir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara monte dans le bus avec papa. Le chauffeur ouvre la porte.
-papa|C'est un métier.
-narrateur|Le chauffeur fait un geste utile. Il conduit.
-enfant-f|Chauffeur. Ils descendent. Ça sent le pain chaud.
-narrateur|Le boulanger pose les brioches.
-papa|C'est un métier.
-narrateur|Le boulanger fait un geste utile. Il prépare le pain.
-enfant-f|Boulanger. Plus tard, ils passent chez le médecin.
-narrateur|Le médecin écoute le cœur. C'est un métier. Un geste utile. Il soigne. À l'école, la maîtresse lit. C'est un métier. Un geste utile. Elle aide les enfants. Sara nomme chaque métier. Parce qu'elle nomme, elle comprend le geste.</t>
+          <t>narrateur|La poupée penche sur la chaise de bois.
+narrateur|Un petit pansement se décolle au genou.
+narrateur|Le tissu est froissé, un peu gris.
+narrateur|La chambre sent encore le linge propre.
+narrateur|Un rayon passe sur le parquet.
+narrateur|Sarah vit ici, avec papa.
+enfant-f|Elle a un bob, papa.
+papa|Au genou de la poupée ?
+enfant-f|Oui.
+enfant-f|Je veux la consoler.
+narrateur|Sarah pose sa main sur le genou de tissu.
+narrateur|Le tissu est rêche, un peu froid.
+papa|Le pansement ne tient plus.
+papa|On va chez le médecin du village ?
+enfant-f|Pour la poupée ?
+papa|Pour la poupée.
+papa|Et pour toi, si ça pique.
+narrateur|En ce moment, Sarah serre la poupée.
+narrateur|Le bras de chiffon pend un peu.
+narrateur|Ils descendent l'escalier de pierre.
+narrateur|Dehors, le tilleul sent le miel.
+narrateur|Un oiseau saute dans l'herbe.
+enfant-f|Elle a mal, je crois.
+papa|On marche doucement.
+papa|Tu la tiens bien ?
+enfant-f|Oui, papa.
+narrateur|La plaque du médecin brille au soleil.
+narrateur|Elle est ronde, un peu chaude.
+narrateur|La porte sent le savon clair.
+papa|On frappe, tout doux.
+narrateur|Toc, toc.
+narrateur|Le médecin ouvre.
+narrateur|Sa blouse est blanche, un peu froissée.
+enfant-f|Ma poupée a un bob.
+papa|Sarah veut la consoler.
+papa|C'est le médecin.
+papa|C'est son métier.
+enfant-f|Médecin.
+narrateur|Sarah montre le genou de tissu.
+narrateur|Le vieux pansement pend.
+narrateur|Le médecin parle tout bas.
+papa|Il soigne, Sarah.
+papa|Tu restes près de moi ?
+enfant-f|Oui.
+narrateur|Sarah a aussi un petit bob au genou.
+narrateur|Ça pique, tout doux, rien de grave.
+enfant-f|Moi aussi, un peu.
+papa|On montre, sans courir.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1352,12 +1403,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le chauffeur conduit le bus. C'est quoi ?</t>
+          <t>Le médecin soigne le genou. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le chauffeur conduit le bus. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le médecin soigne le genou. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,12 +1418,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>un métier</t>
+          <t>métier</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>un métier | métier | chauffeur | le chauffeur</t>
+          <t>métier | un métier | son métier | le métier | c'est un métier</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1387,7 +1438,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il fait un geste utile. C'est quoi ?</t>
+          <t>Il soigne. C'est quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1436,7 +1487,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le chauffeur conduit le bus. C'est quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le médecin soigne le genou.
+narrateur|C'est quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
+          <t>Le médecin pose un pansement neuf. D'abord sur le genou de Sarah. Le tissu est doux, un peu frais. Il est froid. Oui. Il tient bien. Ensuite, un tout petit pansement. Pour le genou de la poupée. Sarah appuie le bord, tout doux. Voilà. Bravo, Sarah. Tu as consolé la poupée. Le médecin t'a aidée. Merci. Merci. C'est son métier. Il soigne. La poupée tient droite, contre l'épaule. Le rayon revient sur la blouse. On rentre, les deux genoux au chaud ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara a nommé les &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;s. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le médecin pose un pansement neuf. D'abord sur le genou de Sarah. Le tissu est doux, un peu frais. Il est froid. Oui. Il tient bien. Ensuite, un tout petit pansement. Pour le genou de la poupée. Sarah appuie le bord, tout doux. Voilà. Bravo, Sarah. Tu as consolé la poupée. Le médecin t'a aidée. Merci. Merci. C'est son métier. Il soigne. La poupée tient droite, contre l'épaule. Le rayon revient sur la blouse. On rentre, les deux genoux au chaud ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1604,7 +1655,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1731,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le médecin pose un pansement neuf.
+narrateur|D'abord sur le genou de Sarah.
+narrateur|Le tissu est doux, un peu frais.
+enfant-f|Il est froid.
+papa|Oui.
+papa|Il tient bien.
+narrateur|Ensuite, un tout petit pansement.
+narrateur|Pour le genou de la poupée.
+narrateur|Sarah appuie le bord, tout doux.
+enfant-f|Voilà.
+papa|Bravo, Sarah.
+papa|Tu as consolé la poupée.
+papa|Le médecin t'a aidée.
+enfant-f|Merci.
+papa|Merci.
+papa|C'est son métier.
+enfant-f|Il soigne.
+narrateur|La poupée tient droite, contre l'épaule.
+narrateur|Le rayon revient sur la blouse.
+papa|On rentre, les deux genoux au chaud ?
+enfant-f|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sara serre la main de papa. Ils rentrent à la maison.</t>
+          <t>Ils reprennent le chemin du tilleul. Les feuilles bougent, tout léger. Sarah marche sans se presser. La poupée regarde le ciel, un peu de travers. Elle n'a plus mal. Toi non plus ? Ça pique moins. Bien. La chaise de bois attend dans la chambre. Sarah assied la poupée. Le pansement tient, tout droit. Tu lui parles ? Tu es brave, poupée. Et toi aussi. Sarah pose sa main sur les deux genoux. Le sien, et celui de chiffon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils reprennent le chemin du tilleul. Les feuilles bougent, tout léger. Sarah marche sans se presser. La poupée regarde le ciel, un peu de travers. Elle n'a plus mal. Toi non plus ? Ça pique moins. Bien. La chaise de bois attend dans la chambre. Sarah assied la poupée. Le pansement tient, tout droit. Tu lui parles ? Tu es brave, poupée. Et toi aussi. Sarah pose sa main sur les deux genoux. Le sien, et celui de chiffon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1776,7 +1846,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1918,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sara serre la main de papa. Ils rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils reprennent le chemin du tilleul.
+narrateur|Les feuilles bougent, tout léger.
+narrateur|Sarah marche sans se presser.
+narrateur|La poupée regarde le ciel, un peu de travers.
+enfant-f|Elle n'a plus mal.
+papa|Toi non plus ?
+enfant-f|Ça pique moins.
+papa|Bien.
+narrateur|La chaise de bois attend dans la chambre.
+narrateur|Sarah assied la poupée.
+narrateur|Le pansement tient, tout droit.
+papa|Tu lui parles ?
+enfant-f|Tu es brave, poupée.
+papa|Et toi aussi.
+narrateur|Sarah pose sa main sur les deux genoux.
+narrateur|Le sien, et celui de chiffon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le rayon revient sur le parquet. Le linge sent encore le propre. Elle est consolée. Oui. Le médecin a bien travaillé. La poupée penche moins, sur la chaise. Le petit pansement reste collé, tout calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rayon revient sur le parquet. Le linge sent encore le propre. Elle est consolée. Oui. Le médecin a bien travaillé. La poupée penche moins, sur la chaise. Le petit pansement reste collé, tout calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,14 +2021,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2100,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le rayon revient sur le parquet.
+narrateur|Le linge sent encore le propre.
+enfant-f|Elle est consolée.
+papa|Oui.
+papa|Le médecin a bien travaillé.
+narrateur|La poupée penche moins, sur la chaise.
+narrateur|Le petit pansement reste collé, tout calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-02.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bus, boulangerie, chez le médecin, école</t>
+          <t>chambre, chemin du tilleul, cabinet du médecin du village</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
